--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2020_coquimbo.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2020_coquimbo.xlsx
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 13:40</t>
+    <t xml:space="preserve">2026-09-09 19:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2020_coquimbo.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2020_coquimbo.xlsx
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 19:59</t>
+    <t xml:space="preserve">2026-09-18 17:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2020_coquimbo.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2020_coquimbo.xlsx
@@ -30,51 +30,51 @@
     <t xml:space="preserve">Cobertura</t>
   </si>
   <si>
+    <t xml:space="preserve">Paihuano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Río Hurtado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Punitaqui</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andacollo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Higuera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vicuña</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Illapel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Combarbalá</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Vilos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salamanca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monte Patria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ovalle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coquimbo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Serena</t>
+  </si>
+  <si>
     <t xml:space="preserve">Canela</t>
   </si>
   <si>
-    <t xml:space="preserve">La Serena</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coquimbo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ovalle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monte Patria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Salamanca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los Vilos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Combarbalá</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Illapel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vicuña</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Higuera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Andacollo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Punitaqui</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Río Hurtado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paihuano</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 17:03</t>
+    <t xml:space="preserve">2026-09-27 21:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -504,13 +504,13 @@
         <v>4</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>8253</v>
+        <v>5066</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>9546</v>
+        <v>4675</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>86.46</v>
+        <v>108.36</v>
       </c>
     </row>
     <row r="3">
@@ -518,13 +518,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>221888</v>
+        <v>4620</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>249656</v>
+        <v>4372</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>88.88</v>
+        <v>105.67</v>
       </c>
     </row>
     <row r="4">
@@ -532,13 +532,13 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>241317</v>
+        <v>12727</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>256735</v>
+        <v>12165</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>93.99</v>
+        <v>104.62</v>
       </c>
     </row>
     <row r="5">
@@ -546,13 +546,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>113990</v>
+        <v>12151</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>121269</v>
+        <v>11791</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>94</v>
+        <v>103.05</v>
       </c>
     </row>
     <row r="6">
@@ -560,13 +560,13 @@
         <v>8</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>30586</v>
+        <v>4582</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>32527</v>
+        <v>4450</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>94.03</v>
+        <v>102.97</v>
       </c>
     </row>
     <row r="7">
@@ -574,13 +574,13 @@
         <v>9</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>28766</v>
+        <v>30167</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>29110</v>
+        <v>29741</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>98.82</v>
+        <v>101.43</v>
       </c>
     </row>
     <row r="8">
@@ -588,13 +588,13 @@
         <v>10</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>23378</v>
+        <v>33181</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>23374</v>
+        <v>32801</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>100.02</v>
+        <v>101.16</v>
       </c>
     </row>
     <row r="9">
@@ -616,13 +616,13 @@
         <v>12</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>33181</v>
+        <v>23378</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>32801</v>
+        <v>23374</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>101.16</v>
+        <v>100.02</v>
       </c>
     </row>
     <row r="11">
@@ -630,13 +630,13 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>30167</v>
+        <v>28766</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>29741</v>
+        <v>29110</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>101.43</v>
+        <v>98.82</v>
       </c>
     </row>
     <row r="12">
@@ -644,13 +644,13 @@
         <v>14</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>4582</v>
+        <v>30586</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>4450</v>
+        <v>32527</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>102.97</v>
+        <v>94.03</v>
       </c>
     </row>
     <row r="13">
@@ -658,13 +658,13 @@
         <v>15</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>12151</v>
+        <v>113990</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>11791</v>
+        <v>121269</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>103.05</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">
@@ -672,13 +672,13 @@
         <v>16</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>12727</v>
+        <v>241317</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>12165</v>
+        <v>256735</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>104.62</v>
+        <v>93.99</v>
       </c>
     </row>
     <row r="15">
@@ -686,13 +686,13 @@
         <v>17</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>4620</v>
+        <v>221888</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>4372</v>
+        <v>249656</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>105.67</v>
+        <v>88.88</v>
       </c>
     </row>
     <row r="16">
@@ -700,13 +700,13 @@
         <v>18</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>5066</v>
+        <v>8253</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>4675</v>
+        <v>9546</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>108.36</v>
+        <v>86.46</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2020_coquimbo.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2020_coquimbo.xlsx
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 21:46</t>
+    <t xml:space="preserve">2026-10-05 05:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
